--- a/reports/二级子公司D_利润表_2025-12.xlsx
+++ b/reports/二级子公司D_利润表_2025-12.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>80893396</v>
+        <v>82664156</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>79111474</v>
+        <v>79141196</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>982539177</v>
+        <v>982071887</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>272344</v>
+        <v>272329</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>3388138</v>
+        <v>3391122</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>231786</v>
+        <v>232858</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2903906</v>
+        <v>2906938</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>195063</v>
+        <v>193567</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>2420052</v>
+        <v>2422233</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>173556</v>
+        <v>173846</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>2177986</v>
+        <v>2179462</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>97563</v>
+        <v>96452</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1209989</v>
+        <v>1210366</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>77214</v>
+        <v>77136</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>968021</v>
+        <v>967883</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>79845870</v>
+        <v>81617968</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>78063948</v>
+        <v>78095008</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>4364044</v>
+        <v>4359169</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>54447589</v>
+        <v>54395879</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>340245</v>
+        <v>339901</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>4235180</v>
+        <v>4230840</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>579717</v>
+        <v>584031</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>7259740</v>
+        <v>7254209</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>70203571</v>
+        <v>70202093</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>871221781</v>
+        <v>870788086</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1157132</v>
+        <v>1170946</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>14519834</v>
+        <v>14519060</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>390300</v>
+        <v>390211</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>4839984</v>
+        <v>4841716</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>1929749</v>
+        <v>1948592</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>24200431</v>
+        <v>24217228</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>486961</v>
+        <v>486154</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>6049818</v>
+        <v>6055709</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1741907</v>
+        <v>1745844</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>21780855</v>
+        <v>21801986</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>40015</v>
+        <v>39898</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>479976</v>
+        <v>480481</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1042836</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>13076203</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>694382</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>8714155</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>53167748</v>
+        <v>56494345</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>47707090</v>
+        <v>47276489</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>46838928</v>
+        <v>46404366</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>580800616</v>
+        <v>580299457</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>868162</v>
+        <v>872123</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>10890151</v>
+        <v>10879082</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1748636</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>21758934</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>560820</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>6964291</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>351067</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>4354163</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>421551</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>5227157</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>316035</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>3921998</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>210399</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>2615565</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>174961</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>2180098</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>829442</v>
+        <v>824148</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>10285056</v>
+        <v>10295331</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>626879</v>
+        <v>628707</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>7865075</v>
+        <v>7871840</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>487349</v>
+        <v>482691</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>6049859</v>
+        <v>6053523</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>3673490</v>
+        <v>3664475</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>45981581</v>
+        <v>45988823</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>150234</v>
+        <v>144643</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1799925</v>
+        <v>1814577</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>320143</v>
+        <v>318430</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>3840169</v>
+        <v>3837297</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>359134</v>
+        <v>318430</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>4319819</v>
+        <v>3837297</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>40164</v>
+        <v>39973</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>480017</v>
+        <v>479458</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>162297</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1941938</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>306777</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>3808745</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>108593</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1295482</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>81486</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>972069</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>135736</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1620858</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>438223</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>5449291</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>72126</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>864953</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>53959</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>648723</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>89718</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1081008</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>62688</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>756445</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>44734</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>540073</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>35791</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>431854</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>26873</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>323758</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>26678122</v>
+        <v>26210699</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>30638156</v>
+        <v>29055582</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>174976</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>2175979</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>45192</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>539593</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>70220</v>
+        <v>70393</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>840032</v>
+        <v>839713</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>26607902</v>
+        <v>26315282</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2514121</v>
+        <v>2513259</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>30000546</v>
+        <v>30017555</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>24093781</v>
+        <v>23802023</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>24093781</v>
+        <v>23802023</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>24093781</v>
+        <v>23802023</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>24093781</v>
+        <v>23802023</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>24093781</v>
+        <v>23802023</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
